--- a/data/processed/positivacao/2025-02_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-02_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26245,7 +26245,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B997" t="inlineStr"/>
@@ -37415,7 +37415,7 @@
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr"/>
@@ -65917,7 +65917,7 @@
     <row r="2524">
       <c r="A2524" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2524" t="inlineStr"/>
@@ -67588,12 +67588,12 @@
       <c r="A2589" t="inlineStr"/>
       <c r="B2589" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 3 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 1.336,84
+          <t>Vendedor 1 - VENDEDOR 01: positivou 3 cliente(s), não positivou 88 cliente(s) - Total vendido: R$ 1.336,84
 Vendedor 18 - LOJA: positivou 197 cliente(s), não positivou 699 cliente(s) - Total vendido: R$ 73.443,19
-Vendedor 3 - FERNANDA: positivou 109 cliente(s), não positivou 320 cliente(s) - Total vendido: R$ 143.000,20
-Vendedor 4 - DANIELA: positivou 109 cliente(s), não positivou 534 cliente(s) - Total vendido: R$ 56.475,41
+Vendedor 3 - VENDEDOR 03: positivou 109 cliente(s), não positivou 320 cliente(s) - Total vendido: R$ 143.000,20
+Vendedor 4 - VENDEDOR 04: positivou 109 cliente(s), não positivou 534 cliente(s) - Total vendido: R$ 56.475,41
 Vendedor 5 - SITE: positivou 3 cliente(s), não positivou 449 cliente(s) - Total vendido: R$ 410,84
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2589" t="inlineStr"/>
